--- a/Shiny/Datos limpios/pricing_semanal_historico.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_historico.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J572"/>
+  <dimension ref="A1:J575"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -18455,10 +18455,10 @@
         <v>19838.64</v>
       </c>
       <c r="I565">
-        <v>368355.97</v>
+        <v>368215.29</v>
       </c>
       <c r="J565">
-        <v>1994882.79</v>
+        <v>1994742.11</v>
       </c>
     </row>
     <row r="566">
@@ -18487,10 +18487,10 @@
         <v>28907.18</v>
       </c>
       <c r="I566">
-        <v>520891.25</v>
+        <v>520857.33</v>
       </c>
       <c r="J566">
-        <v>1972655.94</v>
+        <v>1972622.02</v>
       </c>
     </row>
     <row r="567">
@@ -18513,16 +18513,16 @@
         <v>639784.35</v>
       </c>
       <c r="G567">
-        <v>4617338.97</v>
+        <v>4615992.54</v>
       </c>
       <c r="H567">
         <v>16898.25</v>
       </c>
       <c r="I567">
-        <v>594174.1399999999</v>
+        <v>592986.4099999999</v>
       </c>
       <c r="J567">
-        <v>6251514.619999999</v>
+        <v>6248980.46</v>
       </c>
     </row>
     <row r="568">
@@ -18545,16 +18545,16 @@
         <v>395206.84</v>
       </c>
       <c r="G568">
-        <v>2298314.3</v>
+        <v>2298163.85</v>
       </c>
       <c r="H568">
         <v>35504.45</v>
       </c>
       <c r="I568">
-        <v>335583.54</v>
+        <v>335171.96</v>
       </c>
       <c r="J568">
-        <v>3242966.96</v>
+        <v>3242404.93</v>
       </c>
     </row>
     <row r="569">
@@ -18577,16 +18577,16 @@
         <v>304012.16</v>
       </c>
       <c r="G569">
-        <v>1169573.25</v>
+        <v>1169453.25</v>
       </c>
       <c r="H569">
         <v>5781.29</v>
       </c>
       <c r="I569">
-        <v>489653.0699999999</v>
+        <v>489497.7999999999</v>
       </c>
       <c r="J569">
-        <v>2082240.08</v>
+        <v>2081964.81</v>
       </c>
     </row>
     <row r="570">
@@ -18612,13 +18612,13 @@
         <v>601842.1599999999</v>
       </c>
       <c r="H570">
-        <v>22638.86</v>
+        <v>21638.86</v>
       </c>
       <c r="I570">
-        <v>773596.66</v>
+        <v>773300.1</v>
       </c>
       <c r="J570">
-        <v>1998562.06</v>
+        <v>1997265.5</v>
       </c>
     </row>
     <row r="571">
@@ -18664,25 +18664,121 @@
         <v>45957</v>
       </c>
       <c r="D572">
-        <v>7950</v>
+        <v>102278.83</v>
       </c>
       <c r="E572">
-        <v>950</v>
+        <v>59661.56</v>
       </c>
       <c r="F572">
-        <v>1510</v>
+        <v>554294.73</v>
       </c>
       <c r="G572">
-        <v>2677.84</v>
+        <v>353649.61</v>
       </c>
       <c r="H572">
-        <v>0</v>
+        <v>13062</v>
       </c>
       <c r="I572">
-        <v>960</v>
+        <v>399832.23</v>
       </c>
       <c r="J572">
-        <v>14047.84</v>
+        <v>1482778.96</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573">
+        <v>2025</v>
+      </c>
+      <c r="B573">
+        <v>45</v>
+      </c>
+      <c r="C573" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D573">
+        <v>124568.03</v>
+      </c>
+      <c r="E573">
+        <v>65910.09999999999</v>
+      </c>
+      <c r="F573">
+        <v>874205.9600000001</v>
+      </c>
+      <c r="G573">
+        <v>473276.52</v>
+      </c>
+      <c r="H573">
+        <v>13193.05</v>
+      </c>
+      <c r="I573">
+        <v>405527.27</v>
+      </c>
+      <c r="J573">
+        <v>1956680.93</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574">
+        <v>2025</v>
+      </c>
+      <c r="B574">
+        <v>46</v>
+      </c>
+      <c r="C574" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D574">
+        <v>77703.97</v>
+      </c>
+      <c r="E574">
+        <v>56736.91</v>
+      </c>
+      <c r="F574">
+        <v>1014195.06</v>
+      </c>
+      <c r="G574">
+        <v>333538.6299999999</v>
+      </c>
+      <c r="H574">
+        <v>7740.780000000001</v>
+      </c>
+      <c r="I574">
+        <v>600952.0399999999</v>
+      </c>
+      <c r="J574">
+        <v>2090867.39</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575">
+        <v>2025</v>
+      </c>
+      <c r="B575">
+        <v>47</v>
+      </c>
+      <c r="C575" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D575">
+        <v>125853.85</v>
+      </c>
+      <c r="E575">
+        <v>43395.28</v>
+      </c>
+      <c r="F575">
+        <v>384460.97</v>
+      </c>
+      <c r="G575">
+        <v>351428.9399999999</v>
+      </c>
+      <c r="H575">
+        <v>3714.14</v>
+      </c>
+      <c r="I575">
+        <v>487343.15</v>
+      </c>
+      <c r="J575">
+        <v>1396196.33</v>
       </c>
     </row>
   </sheetData>
